--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\Projets_et_Repos\instrumentation-amplifier\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C602F1E-AE24-415D-8D37-2E16B65D3921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0575A85B-C36A-44DB-93F4-9191B5A5DC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{B16C9B84-40CB-4384-9929-CD90A5EEF1D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="131">
   <si>
     <t>DESIGNATOR</t>
   </si>
@@ -269,7 +270,169 @@
     <t>R11</t>
   </si>
   <si>
-    <t>Res 5 kOhm, 5%</t>
+    <t>ORDER</t>
+  </si>
+  <si>
+    <t>Res 5 kOhm( 300Ohm), 5% (4.7k + 300 Ohm)</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ca/short/h98hvh78</t>
+  </si>
+  <si>
+    <t>DigiKey - Shopping Cart</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Part Number</t>
+  </si>
+  <si>
+    <t>Manufacturer Part Number</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Customer Reference</t>
+  </si>
+  <si>
+    <t>Available</t>
+  </si>
+  <si>
+    <t>Backorder</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Extended Price USD</t>
+  </si>
+  <si>
+    <t>CF14JT1K00CT-ND</t>
+  </si>
+  <si>
+    <t>CF14JT1K00</t>
+  </si>
+  <si>
+    <t>RES 1K OHM 5% 1/4W AXIAL</t>
+  </si>
+  <si>
+    <t>CF14JT200RCT-ND</t>
+  </si>
+  <si>
+    <t>CF14JT200R</t>
+  </si>
+  <si>
+    <t>RES 200 OHM 5% 1/4W AXIAL</t>
+  </si>
+  <si>
+    <t>S9337-ND</t>
+  </si>
+  <si>
+    <t>QPC02SXGN-RC</t>
+  </si>
+  <si>
+    <t>CONN JUMPER SHORTING .100" GOLD</t>
+  </si>
+  <si>
+    <t>A19890-ND</t>
+  </si>
+  <si>
+    <t>640445-3</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 3POS 3.96MM</t>
+  </si>
+  <si>
+    <t>1189-2322-ND</t>
+  </si>
+  <si>
+    <t>50YXJ10M5X11</t>
+  </si>
+  <si>
+    <t>CAP ALUM 10UF 20% 50V RADIAL TH</t>
+  </si>
+  <si>
+    <t>CF14JT220RCT-ND</t>
+  </si>
+  <si>
+    <t>CF14JT220R</t>
+  </si>
+  <si>
+    <t>RES 220 OHM 5% 1/4W AXIAL</t>
+  </si>
+  <si>
+    <t>399-C320C105K5N5TA-ND</t>
+  </si>
+  <si>
+    <t>C320C105K5N5TA</t>
+  </si>
+  <si>
+    <t>CAP CER 1UF 50V X8L RADIAL</t>
+  </si>
+  <si>
+    <t>399-4150-ND</t>
+  </si>
+  <si>
+    <t>C315C103M5U5TA</t>
+  </si>
+  <si>
+    <t>CAP CER 10000PF 50V Z5U RADIAL</t>
+  </si>
+  <si>
+    <t>CF14JT10K0CT-ND</t>
+  </si>
+  <si>
+    <t>CF14JT10K0</t>
+  </si>
+  <si>
+    <t>RES 10K OHM 5% 1/4W AXIAL</t>
+  </si>
+  <si>
+    <t>CF14JT4K70CT-ND</t>
+  </si>
+  <si>
+    <t>CF14JT4K70</t>
+  </si>
+  <si>
+    <t>RES 4.7K OHM 5% 1/4W AXIAL</t>
+  </si>
+  <si>
+    <t>CF14JT3K30CT-ND</t>
+  </si>
+  <si>
+    <t>CF14JT3K30</t>
+  </si>
+  <si>
+    <t>RES 3.3K OHM 5% 1/4W AXIAL</t>
+  </si>
+  <si>
+    <t>CF14JT300RCT-ND</t>
+  </si>
+  <si>
+    <t>CF14JT300R</t>
+  </si>
+  <si>
+    <t>RES 300 OHM 5% 1/4W AXIAL</t>
+  </si>
+  <si>
+    <t>399-4151-ND</t>
+  </si>
+  <si>
+    <t>C315C104M5U5TA</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 50V Z5U RADIAL</t>
+  </si>
+  <si>
+    <t>296-1784-5-ND</t>
+  </si>
+  <si>
+    <t>IC OPAMP JFET 4 CIRCUIT 14DIP</t>
   </si>
 </sst>
 </file>
@@ -285,7 +448,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -295,6 +458,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -363,13 +538,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -377,9 +554,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -391,6 +565,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -725,18 +901,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F94120D-FE05-4997-AFD8-90FEF7455658}">
-  <dimension ref="A4:I57"/>
+  <dimension ref="A4:J59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -744,28 +920,31 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -776,200 +955,248 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="I5" s="5"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>10</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" ht="30">
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" ht="30">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="B7" s="1">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1">
+        <v>50</v>
+      </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>25</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
+        <v>10</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="8" t="s">
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="10"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" ht="30">
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>50</v>
+      </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="8" t="s">
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
+        <v>20</v>
+      </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="1"/>
+      <c r="G15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" ht="30">
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="11">
+        <v>20</v>
+      </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="1"/>
+      <c r="G16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="C17" s="10"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+      <c r="C18" s="10"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="2"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -979,8 +1206,9 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -990,21 +1218,23 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="7" t="s">
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
         <v>33</v>
       </c>
@@ -1015,466 +1245,534 @@
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="I22" s="5"/>
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="C23" s="10"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="1"/>
+      <c r="G23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
+      <c r="C24" s="10"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="1"/>
+      <c r="G24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
+      <c r="C25" s="10"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="1"/>
+      <c r="G25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" ht="30">
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
+      <c r="C26" s="10"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="1"/>
+      <c r="G26" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="B27" s="1">
+        <v>2</v>
+      </c>
+      <c r="C27" s="1">
+        <v>25</v>
+      </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="1"/>
+      <c r="G27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="7" t="s">
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
+      <c r="B29" s="1">
+        <v>2</v>
+      </c>
+      <c r="C29" s="1">
+        <v>25</v>
+      </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
+      <c r="B30" s="1">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1">
+        <v>10</v>
+      </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="1"/>
+      <c r="G30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
+      <c r="C31" s="10"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="1"/>
+      <c r="G31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="3" t="s">
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
+      <c r="C32" s="10"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="1"/>
+      <c r="G32" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
+      <c r="C33" s="10"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="1"/>
+      <c r="G33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
+      <c r="B34" s="1">
+        <v>2</v>
+      </c>
+      <c r="C34" s="1">
+        <v>25</v>
+      </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="1"/>
+      <c r="G34" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1">
+        <v>10</v>
+      </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="1"/>
+      <c r="G35" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="7" t="s">
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1">
+        <v>50</v>
+      </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="1"/>
+      <c r="G37" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="3" t="s">
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
+      <c r="C38" s="10"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="1"/>
+      <c r="G38" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
+      <c r="C39" s="10"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="1"/>
+      <c r="G39" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="7" t="s">
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
+      <c r="C41" s="10"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="1"/>
+      <c r="G41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="1:9">
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
+      <c r="C42" s="10"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="1"/>
+      <c r="G42" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
+      <c r="C43" s="10"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="1"/>
+      <c r="G43" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
+      <c r="C44" s="10"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="1"/>
+      <c r="G44" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
+      <c r="B45" s="1">
+        <v>2</v>
+      </c>
+      <c r="C45" s="1">
+        <v>25</v>
+      </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="1"/>
+      <c r="G45" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="1:9">
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
+      <c r="B46" s="1">
+        <v>2</v>
+      </c>
+      <c r="C46" s="10"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="1"/>
+      <c r="G46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
+      <c r="B47" s="1">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1">
+        <v>25</v>
+      </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="1"/>
+      <c r="G47" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
-    </row>
-    <row r="48" spans="1:9">
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
+      <c r="B48" s="1">
+        <v>2</v>
+      </c>
+      <c r="C48" s="10"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="1"/>
+      <c r="G48" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
-    </row>
-    <row r="49" spans="1:9">
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
+      <c r="C49" s="10"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="1"/>
+      <c r="G49" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="7" t="s">
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="3" t="s">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
+      <c r="C51" s="10"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="1"/>
+      <c r="G51" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="3" t="s">
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
+      <c r="C52" s="10"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="1"/>
+      <c r="G52" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-    </row>
-    <row r="53" spans="1:9">
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
+      <c r="C53" s="10"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="1"/>
+      <c r="G53" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-    </row>
-    <row r="54" spans="1:9">
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="4" t="s">
         <v>73</v>
       </c>
@@ -1485,39 +1783,46 @@
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
-      <c r="I54" s="6"/>
-    </row>
-    <row r="55" spans="1:9" ht="45">
+      <c r="I54" s="5"/>
+      <c r="J54" s="6"/>
+    </row>
+    <row r="55" spans="1:10" ht="30">
       <c r="A55" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
+      <c r="C55" s="10"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="1"/>
+      <c r="G55" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
-    </row>
-    <row r="56" spans="1:9">
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
+      <c r="B56" s="1">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1">
+        <v>10</v>
+      </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="1:9">
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" s="2"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -1527,20 +1832,479 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>78</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="A54:I54"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A54:J54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90DFBBC-F74D-4027-804E-93369395249F}">
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3">
+        <v>50</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="J3">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="J4">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J5">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0.21</v>
+      </c>
+      <c r="J6">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0.185</v>
+      </c>
+      <c r="J7">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8">
+        <v>25</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="J8">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0.53700000000000003</v>
+      </c>
+      <c r="J9">
+        <v>5.37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="J10">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11">
+        <v>50</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="J11">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12">
+        <v>25</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="J12">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13">
+        <v>25</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="J13">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>2.7E-2</v>
+      </c>
+      <c r="J14">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="J15">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>130</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="J16">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\Projets_et_Repos\instrumentation-amplifier\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0575A85B-C36A-44DB-93F4-9191B5A5DC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F313C976-914A-4553-B6F6-059E8E516359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{B16C9B84-40CB-4384-9929-CD90A5EEF1D2}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11235" xr2:uid="{B16C9B84-40CB-4384-9929-CD90A5EEF1D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -439,7 +439,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,7 +448,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -470,6 +470,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -538,15 +544,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -565,8 +570,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -902,7 +909,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F94120D-FE05-4997-AFD8-90FEF7455658}">
   <dimension ref="A4:J59"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
@@ -912,7 +919,7 @@
     <col min="10" max="10" width="35.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -944,21 +951,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="7"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -978,7 +985,7 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="30">
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -998,7 +1005,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -1018,7 +1025,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -1038,28 +1045,28 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -1070,14 +1077,14 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="12">
         <v>5</v>
       </c>
       <c r="D12" s="1"/>
@@ -1090,7 +1097,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
@@ -1110,21 +1117,21 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="9"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -1144,14 +1151,14 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="4">
         <v>20</v>
       </c>
       <c r="D16" s="1"/>
@@ -1164,12 +1171,12 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="1"/>
-      <c r="C17" s="10"/>
+      <c r="C17" s="3"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1180,12 +1187,12 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="1"/>
-      <c r="C18" s="10"/>
+      <c r="C18" s="12"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -1196,7 +1203,7 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1208,7 +1215,7 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1220,40 +1227,40 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="4" t="s">
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="7"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="1"/>
-      <c r="C23" s="10"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1264,12 +1271,12 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="1"/>
-      <c r="C24" s="10"/>
+      <c r="C24" s="3"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -1280,12 +1287,12 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B25" s="1"/>
-      <c r="C25" s="10"/>
+      <c r="C25" s="3"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -1296,12 +1303,12 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="1"/>
-      <c r="C26" s="10"/>
+      <c r="C26" s="3"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1312,7 +1319,7 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
@@ -1332,21 +1339,21 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>40</v>
       </c>
@@ -1366,7 +1373,7 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>41</v>
       </c>
@@ -1386,12 +1393,12 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B31" s="1"/>
-      <c r="C31" s="10"/>
+      <c r="C31" s="3"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -1402,12 +1409,12 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B32" s="1"/>
-      <c r="C32" s="10"/>
+      <c r="C32" s="3"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -1418,12 +1425,12 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B33" s="1"/>
-      <c r="C33" s="10"/>
+      <c r="C33" s="3"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -1434,7 +1441,7 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>46</v>
       </c>
@@ -1454,7 +1461,7 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>48</v>
       </c>
@@ -1474,21 +1481,21 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="3" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>52</v>
       </c>
@@ -1508,12 +1515,12 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B38" s="1"/>
-      <c r="C38" s="10"/>
+      <c r="C38" s="3"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -1524,12 +1531,12 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B39" s="1"/>
-      <c r="C39" s="10"/>
+      <c r="C39" s="3"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -1540,26 +1547,26 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="3" t="s">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-    </row>
-    <row r="41" spans="1:10">
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="10"/>
+      <c r="C41" s="3"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -1570,12 +1577,12 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B42" s="1"/>
-      <c r="C42" s="10"/>
+      <c r="C42" s="3"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -1586,12 +1593,12 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B43" s="1"/>
-      <c r="C43" s="10"/>
+      <c r="C43" s="3"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -1602,12 +1609,12 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B44" s="1"/>
-      <c r="C44" s="10"/>
+      <c r="C44" s="3"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -1618,7 +1625,7 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>61</v>
       </c>
@@ -1638,14 +1645,14 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B46" s="1">
         <v>2</v>
       </c>
-      <c r="C46" s="10"/>
+      <c r="C46" s="3"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -1656,7 +1663,7 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>63</v>
       </c>
@@ -1676,14 +1683,14 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B48" s="1">
         <v>2</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="3"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -1694,12 +1701,12 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B49" s="1"/>
-      <c r="C49" s="10"/>
+      <c r="C49" s="3"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -1710,26 +1717,26 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="3" t="s">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-    </row>
-    <row r="51" spans="1:10">
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B51" s="1"/>
-      <c r="C51" s="10"/>
+      <c r="C51" s="3"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -1740,12 +1747,12 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B52" s="1"/>
-      <c r="C52" s="10"/>
+      <c r="C52" s="3"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -1756,12 +1763,12 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B53" s="1"/>
-      <c r="C53" s="10"/>
+      <c r="C53" s="3"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -1772,26 +1779,26 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="1:10">
-      <c r="A54" s="4" t="s">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="6"/>
-    </row>
-    <row r="55" spans="1:10" ht="30">
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="7"/>
+    </row>
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B55" s="1"/>
-      <c r="C55" s="10"/>
+      <c r="C55" s="3"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -1802,7 +1809,7 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>75</v>
       </c>
@@ -1822,7 +1829,7 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -1834,23 +1841,23 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A54:J54"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A50:J50"/>
-    <mergeCell ref="A54:J54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1859,14 +1866,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90DFBBC-F74D-4027-804E-93369395249F}">
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="24.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
@@ -1898,7 +1908,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1927,7 +1937,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1956,7 +1966,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1985,7 +1995,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2014,7 +2024,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2043,7 +2053,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2072,7 +2082,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2101,7 +2111,7 @@
         <v>5.37</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2130,7 +2140,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2159,7 +2169,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2188,7 +2198,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2217,7 +2227,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2246,7 +2256,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2275,7 +2285,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
